--- a/autres/BDD-Skilleat.xlsx
+++ b/autres/BDD-Skilleat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AFCI\Documents\Skilleat\autres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A79D9C-3BEA-475F-9F84-512F52DD4D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87AAE0-32DA-49A9-ACFE-0368700898A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{5E100F81-54E2-4036-BFD6-3583D6F8B6A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{5E100F81-54E2-4036-BFD6-3583D6F8B6A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Chef" sheetId="1" r:id="rId1"/>
